--- a/1318_Cuenca_Tambo/_raw_reportes_xlsx/IDConfig_64911_completo.xlsx
+++ b/1318_Cuenca_Tambo/_raw_reportes_xlsx/IDConfig_64911_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd26f2e404a414fa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc919ab18e9ff4eec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1412</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2910</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2424</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2424</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/1318_Cuenca_Tambo/_raw_reportes_xlsx/IDConfig_64911_completo.xlsx
+++ b/1318_Cuenca_Tambo/_raw_reportes_xlsx/IDConfig_64911_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc919ab18e9ff4eec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R04ca0361129343c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8225</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0391</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.8641</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.0162</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.4079</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.2558</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.8641</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.0162</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.2558</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0391</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0391</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0391</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8871</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1912</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8870</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7349</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6918</x:v>
+        <x:v>      7.5829</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.6918</x:v>
+        <x:v>      7.5829</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.1412</x:v>
+        <x:v>      8.0391</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7404</x:v>
+        <x:v>      8.6475</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.8902</x:v>
+        <x:v>      8.7995</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.2910</x:v>
+        <x:v>      8.1912</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2424</x:v>
+        <x:v>      7.1266</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2424</x:v>
+        <x:v>      7.1266</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0926</x:v>
+        <x:v>      6.9746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.7930</x:v>
+        <x:v>      6.6704</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0926</x:v>
+        <x:v>      6.9746</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.2424</x:v>
+        <x:v>      7.1266</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.3922</x:v>
+        <x:v>      7.2787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.8416</x:v>
+        <x:v>      7.7349</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.9914</x:v>
+        <x:v>      7.8870</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.2910</x:v>
+        <x:v>      8.1912</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.4408</x:v>
+        <x:v>      8.3433</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.5906</x:v>
+        <x:v>      8.4954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.8902</x:v>
+        <x:v>      8.7996</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.0400</x:v>
+        <x:v>      8.9516</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.0400</x:v>
+        <x:v>      8.9516</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.6392</x:v>
+        <x:v>      9.5599</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.4894</x:v>
+        <x:v>      9.4079</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.1898</x:v>
+        <x:v>      9.1037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.3396</x:v>
+        <x:v>      9.2558</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.7890</x:v>
+        <x:v>      9.7120</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.0886</x:v>
+        <x:v>     10.0162</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.5380</x:v>
+        <x:v>     10.4724</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.2870</x:v>
+        <x:v>     11.2328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.4368</x:v>
+        <x:v>     11.3848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     10.9874</x:v>
+        <x:v>     10.9286</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.4368</x:v>
+        <x:v>     11.3848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.4368</x:v>
+        <x:v>     11.3848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7364</x:v>
+        <x:v>     11.6890</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.8862</x:v>
+        <x:v>     11.8411</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.7364</x:v>
+        <x:v>     11.6890</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.0360</x:v>
+        <x:v>     11.9931</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.5866</x:v>
+        <x:v>     11.5369</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.0360</x:v>
+        <x:v>     11.9931</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +2079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.1858</x:v>
+        <x:v>     12.1452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.6352</x:v>
+        <x:v>     12.6015</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.7850</x:v>
+        <x:v>     12.7536</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.9348</x:v>
+        <x:v>     12.9057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.8336</x:v>
+        <x:v>     13.8181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +2259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.3199</x:v>
+        <x:v>     14.3133</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     12.9348</x:v>
+        <x:v>     12.9057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.0846</x:v>
+        <x:v>     13.0578</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.2344</x:v>
+        <x:v>     13.2098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +2379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.3842</x:v>
+        <x:v>     13.3619</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.5340</x:v>
+        <x:v>     13.5140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +2409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     13.9834</x:v>
+        <x:v>     13.9702</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.3199</x:v>
+        <x:v>     14.3133</x:v>
       </x:c>
     </x:row>
     <x:row>
